--- a/Data/27/testDataIreland.xlsx
+++ b/Data/27/testDataIreland.xlsx
@@ -1,34 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27928"/>
-  <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7906BC5-5CF6-46C7-94AF-39B387FCC5D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet sheetId="1" name="Sheet1" state="visible" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="109">
   <si>
     <t>TestCaseIDs</t>
   </si>
@@ -204,6 +190,15 @@
     <t>Test_1</t>
   </si>
   <si>
+    <t xml:space="preserve">Test failed for 'Noemy Crooks' Employee:{10699539}TimeoutError: locator.waitFor: Timeout 30000ms exceeded.
+Call log:
+  [2m- waiting for getByRole('button', { name: 'Verify nationality: Onboarding for Noemy Crooks' }).first() to be visible[22m
+</t>
+  </si>
+  <si>
+    <t>Failed</t>
+  </si>
+  <si>
     <t>001 Recruitment (Lubym Wyvyfu (221849))</t>
   </si>
   <si>
@@ -213,10 +208,10 @@
     <t>Mr</t>
   </si>
   <si>
-    <t>Dortha</t>
-  </si>
-  <si>
-    <t>Spencer</t>
+    <t>Noemy</t>
+  </si>
+  <si>
+    <t>Crooks</t>
   </si>
   <si>
     <t>Landline</t>
@@ -285,7 +280,7 @@
     <t>Personal Public Service Number (PPS no)</t>
   </si>
   <si>
-    <t>1234590TW</t>
+    <t>1234727TW</t>
   </si>
   <si>
     <t>Male</t>
@@ -324,16 +319,394 @@
     <t>Test_2</t>
   </si>
   <si>
+    <t xml:space="preserve">Test failed for 'Ollie Moen' Employee:{10699540}TimeoutError: locator.click: Timeout 30000ms exceeded.
+Call log:
+  [2m- waiting for locator('xpath=(//*[@data-automation-id=\'pex-search-result-header\']//a[contains(text(),\'10699540\')])[1]')[22m
+[2m  -   locator resolved to &lt;a data-uxi-rank="0" class="pexsearch-11mf54b" data…&gt;Ollie Moen (10699540)&lt;/a&gt;[22m
+[2m  - attempting click action[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is not stable[22m
+[2m  - retrying click action, attempt #1[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="css-14h3bs2-ActionButtonsContainer ep60xj…&gt;…&lt;/div&gt; from &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #2[22m
+[2m  -   waiting 20ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="css-14h3bs2-ActionButtonsContainer ep60xj…&gt;…&lt;/div&gt; from &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #3[22m
+[2m  -   waiting 100ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; intercepts pointer events[22m
+[2m  - retrying click action, attempt #4[22m
+[2m  -   waiting 100ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; intercepts pointer events[22m
+[2m  - retrying click action, attempt #5[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="css-14h3bs2-ActionButtonsContainer ep60xj…&gt;…&lt;/div&gt; from &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #6[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="css-14h3bs2-ActionButtonsContainer ep60xj…&gt;…&lt;/div&gt; from &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #7[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; intercepts pointer events[22m
+[2m  - retrying click action, attempt #8[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; intercepts pointer events[22m
+[2m  - retrying click action, attempt #9[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="css-14h3bs2-ActionButtonsContainer ep60xj…&gt;…&lt;/div&gt; from &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #10[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="css-14h3bs2-ActionButtonsContainer ep60xj…&gt;…&lt;/div&gt; from &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #11[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; intercepts pointer events[22m
+[2m  - retrying click action, attempt #12[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; intercepts pointer events[22m
+[2m  - retrying click action, attempt #13[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="css-14h3bs2-ActionButtonsContainer ep60xj…&gt;…&lt;/div&gt; from &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #14[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="css-14h3bs2-ActionButtonsContainer ep60xj…&gt;…&lt;/div&gt; from &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #15[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; intercepts pointer events[22m
+[2m  - retrying click action, attempt #16[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; intercepts pointer events[22m
+[2m  - retrying click action, attempt #17[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="css-14h3bs2-ActionButtonsContainer ep60xj…&gt;…&lt;/div&gt; from &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #18[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="css-14h3bs2-ActionButtonsContainer ep60xj…&gt;…&lt;/div&gt; from &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #19[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; intercepts pointer events[22m
+[2m  - retrying click action, attempt #20[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; intercepts pointer events[22m
+[2m  - retrying click action, attempt #21[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="css-14h3bs2-ActionButtonsContainer ep60xj…&gt;…&lt;/div&gt; from &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #22[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="css-14h3bs2-ActionButtonsContainer ep60xj…&gt;…&lt;/div&gt; from &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #23[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; intercepts pointer events[22m
+[2m  - retrying click action, attempt #24[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; intercepts pointer events[22m
+[2m  - retrying click action, attempt #25[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="css-14h3bs2-ActionButtonsContainer ep60xj…&gt;…&lt;/div&gt; from &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #26[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="css-14h3bs2-ActionButtonsContainer ep60xj…&gt;…&lt;/div&gt; from &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #27[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; intercepts pointer events[22m
+[2m  - retrying click action, attempt #28[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; intercepts pointer events[22m
+[2m  - retrying click action, attempt #29[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="css-14h3bs2-ActionButtonsContainer ep60xj…&gt;…&lt;/div&gt; from &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #30[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="css-14h3bs2-ActionButtonsContainer ep60xj…&gt;…&lt;/div&gt; from &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #31[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; intercepts pointer events[22m
+[2m  - retrying click action, attempt #32[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; intercepts pointer events[22m
+[2m  - retrying click action, attempt #33[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="css-14h3bs2-ActionButtonsContainer ep60xj…&gt;…&lt;/div&gt; from &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #34[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="css-14h3bs2-ActionButtonsContainer ep60xj…&gt;…&lt;/div&gt; from &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #35[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; intercepts pointer events[22m
+[2m  - retrying click action, attempt #36[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; intercepts pointer events[22m
+[2m  - retrying click action, attempt #37[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="css-14h3bs2-ActionButtonsContainer ep60xj…&gt;…&lt;/div&gt; from &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #38[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="css-14h3bs2-ActionButtonsContainer ep60xj…&gt;…&lt;/div&gt; from &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #39[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; intercepts pointer events[22m
+[2m  - retrying click action, attempt #40[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; intercepts pointer events[22m
+[2m  - retrying click action, attempt #41[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="css-14h3bs2-ActionButtonsContainer ep60xj…&gt;…&lt;/div&gt; from &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #42[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="css-14h3bs2-ActionButtonsContainer ep60xj…&gt;…&lt;/div&gt; from &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #43[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; intercepts pointer events[22m
+[2m  - retrying click action, attempt #44[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; intercepts pointer events[22m
+[2m  - retrying click action, attempt #45[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="css-14h3bs2-ActionButtonsContainer ep60xj…&gt;…&lt;/div&gt; from &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #46[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="css-14h3bs2-ActionButtonsContainer ep60xj…&gt;…&lt;/div&gt; from &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #47[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; intercepts pointer events[22m
+[2m  - retrying click action, attempt #48[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; intercepts pointer events[22m
+[2m  - retrying click action, attempt #49[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="css-14h3bs2-ActionButtonsContainer ep60xj…&gt;…&lt;/div&gt; from &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #50[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="css-14h3bs2-ActionButtonsContainer ep60xj…&gt;…&lt;/div&gt; from &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #51[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; intercepts pointer events[22m
+[2m  - retrying click action, attempt #52[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; intercepts pointer events[22m
+[2m  - retrying click action, attempt #53[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+</t>
+  </si>
+  <si>
     <t>001 Store Management (Savip Gytape (100446))</t>
   </si>
   <si>
-    <t>Guillermo</t>
-  </si>
-  <si>
-    <t>Harber</t>
-  </si>
-  <si>
-    <t>Auto 82912097</t>
+    <t>Ollie</t>
+  </si>
+  <si>
+    <t>Moen</t>
+  </si>
+  <si>
+    <t>Auto 59907084</t>
   </si>
   <si>
     <t>Department Manager</t>
@@ -342,7 +715,7 @@
     <t>92 Retail Management</t>
   </si>
   <si>
-    <t>1234591TW</t>
+    <t>1234728TW</t>
   </si>
   <si>
     <t>IE Management Group 20</t>
@@ -351,66 +724,66 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="mm/dd/yyyy"/>
   </numFmts>
   <fonts count="8" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
-      <sz val="10"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="10"/>
+      <name val="Calibri"/>
     </font>
     <font>
-      <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
+      <family val="2"/>
+      <scheme val="minor"/>
       <sz val="11"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <color theme="9" tint="-0.249977111117893"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
-      <color theme="9" tint="-0.249977111117893"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
-      <sz val="11"/>
       <color theme="10"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
-      <sz val="11"/>
       <color rgb="FF4A4A4A"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
-      <sz val="11"/>
       <color rgb="FF000000"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="8">
@@ -428,19 +801,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.59999389629810485"/>
+        <fgColor theme="6" tint="0.5999938962981048"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <fgColor theme="0" tint="-0.1499984740745262"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79998168889431442"/>
+        <fgColor theme="5" tint="0.7999816888943144"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -456,7 +829,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -466,25 +839,15 @@
     </border>
     <border>
       <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
     <border>
       <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
+      <right style="thin"/>
+      <top style="thin"/>
       <bottom/>
       <diagonal/>
     </border>
@@ -495,27 +858,15 @@
       <right style="medium">
         <color indexed="64"/>
       </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <top style="thin"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
     <border>
@@ -529,22 +880,11 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -637,10 +977,6 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -921,9 +1257,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:BH3"/>
-  <sheetFormatPr defaultRowHeight="14.5" customHeight="1" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.5" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.35" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="23.6328125" customWidth="1"/>
     <col min="2" max="2" width="68.08984375" customWidth="1"/>
@@ -974,7 +1310,7 @@
     <col min="100" max="100" width="34.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:60" ht="51" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" ht="51" customHeight="1" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1156,279 +1492,287 @@
         <v>56</v>
       </c>
     </row>
-    <row r="2" spans="1:60" ht="87.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" ht="87.5" customHeight="1" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>57</v>
       </c>
-      <c r="B2" s="12"/>
-      <c r="C2" s="13"/>
+      <c r="B2" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="C2" s="13" t="s">
+        <v>59</v>
+      </c>
       <c r="D2" s="14" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E2" s="15" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F2" s="16" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G2" s="17" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="H2" s="17" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="I2" s="18">
         <v>861240232</v>
       </c>
       <c r="J2" s="18" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="K2" s="18" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="L2" s="19">
-        <f t="shared" ref="L2:L3" ca="1" si="0">TODAY()-31</f>
-        <v>45774</v>
+        <f t="shared" ref="L2:L3" si="0">TODAY()-31</f>
+        <v>45779</v>
       </c>
       <c r="M2" s="15" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="N2" s="20" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="O2" s="20" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="P2" s="18">
         <v>38</v>
       </c>
       <c r="Q2" s="18" t="s">
+        <v>68</v>
+      </c>
+      <c r="R2" s="18" t="s">
+        <v>70</v>
+      </c>
+      <c r="S2" s="18" t="s">
+        <v>68</v>
+      </c>
+      <c r="T2" s="18" t="s">
         <v>66</v>
       </c>
-      <c r="R2" s="18" t="s">
-        <v>68</v>
-      </c>
-      <c r="S2" s="18" t="s">
+      <c r="U2" s="21" t="s">
+        <v>71</v>
+      </c>
+      <c r="V2" s="22" t="s">
+        <v>72</v>
+      </c>
+      <c r="W2" s="18" t="s">
         <v>66</v>
       </c>
-      <c r="T2" s="18" t="s">
-        <v>64</v>
-      </c>
-      <c r="U2" s="21" t="s">
-        <v>69</v>
-      </c>
-      <c r="V2" s="22" t="s">
-        <v>70</v>
-      </c>
-      <c r="W2" s="18" t="s">
-        <v>64</v>
-      </c>
       <c r="X2" s="23">
-        <f t="shared" ref="X2:X3" ca="1" si="1">L2</f>
-        <v>45774</v>
+        <f t="shared" ref="X2:X3" si="1">L2</f>
+        <v>45779</v>
       </c>
       <c r="Y2" s="19">
-        <f t="shared" ref="Y2:Y3" ca="1" si="2">X2+90</f>
-        <v>45864</v>
+        <f t="shared" ref="Y2:Y3" si="2">X2+90</f>
+        <v>45869</v>
       </c>
       <c r="Z2" s="18" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="AA2" s="24" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="AB2" s="25" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="AC2" s="26" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AD2" s="25" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="AE2" s="15" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="AF2" s="15" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AG2" s="27">
         <v>37.5</v>
       </c>
       <c r="AH2" s="15" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="AI2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AJ2" s="23" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AK2" s="18" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="AL2" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="AM2" t="s">
+        <v>85</v>
+      </c>
+      <c r="AN2" s="28" t="s">
         <v>82</v>
       </c>
-      <c r="AM2" t="s">
-        <v>83</v>
-      </c>
-      <c r="AN2" s="28" t="s">
-        <v>80</v>
-      </c>
       <c r="AO2" s="28" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AP2" s="28" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="AQ2" s="29" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="AR2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="AS2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="AT2" s="30">
         <v>35591</v>
       </c>
       <c r="AU2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="AV2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="AW2" s="30" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="AX2" s="30" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="AY2" s="30" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="AZ2" s="30" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="BA2" s="30" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="BB2" s="15" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="BC2" s="29" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="BD2" s="29" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="BE2" s="29" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="BF2" s="29" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="BG2" s="18" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="BH2" s="31" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
-    <row r="3" spans="1:60" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" ht="14.5" customHeight="1" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>97</v>
-      </c>
-      <c r="B3" s="32"/>
-      <c r="C3" s="33"/>
+        <v>99</v>
+      </c>
+      <c r="B3" s="32" t="s">
+        <v>100</v>
+      </c>
+      <c r="C3" s="33" t="s">
+        <v>59</v>
+      </c>
       <c r="D3" s="14" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F3" s="16" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G3" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="H3" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="I3" s="18">
         <v>861240232</v>
       </c>
       <c r="J3" s="18" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="K3" s="18" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="L3" s="19">
-        <f t="shared" ca="1" si="0"/>
-        <v>45774</v>
+        <f t="shared" si="0"/>
+        <v>45779</v>
       </c>
       <c r="M3" s="15" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="N3" s="20" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="O3" s="20" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="P3" s="18">
         <v>38</v>
       </c>
       <c r="Q3" s="18" t="s">
+        <v>68</v>
+      </c>
+      <c r="R3" s="18" t="s">
+        <v>70</v>
+      </c>
+      <c r="S3" s="18" t="s">
+        <v>68</v>
+      </c>
+      <c r="T3" s="18" t="s">
         <v>66</v>
       </c>
-      <c r="R3" s="18" t="s">
-        <v>68</v>
-      </c>
-      <c r="S3" s="18" t="s">
+      <c r="U3" s="21" t="s">
+        <v>71</v>
+      </c>
+      <c r="V3" s="22" t="s">
+        <v>72</v>
+      </c>
+      <c r="W3" s="18" t="s">
         <v>66</v>
       </c>
-      <c r="T3" s="18" t="s">
-        <v>64</v>
-      </c>
-      <c r="U3" s="21" t="s">
-        <v>69</v>
-      </c>
-      <c r="V3" s="22" t="s">
-        <v>70</v>
-      </c>
-      <c r="W3" s="18" t="s">
-        <v>64</v>
-      </c>
       <c r="X3" s="23">
-        <f t="shared" ca="1" si="1"/>
-        <v>45774</v>
+        <f t="shared" si="1"/>
+        <v>45779</v>
       </c>
       <c r="Y3" s="19">
-        <f t="shared" ca="1" si="2"/>
-        <v>45864</v>
+        <f t="shared" si="2"/>
+        <v>45869</v>
       </c>
       <c r="Z3" s="18" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="AA3" s="24" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="AB3" s="25" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="AC3" s="26" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="AD3" s="25" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="AE3" s="15" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="AF3" s="15" t="s">
         <v>50</v>
@@ -1437,98 +1781,113 @@
         <v>37.5</v>
       </c>
       <c r="AH3" s="15" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="AI3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AJ3" s="23" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AK3" s="18" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="AL3" s="18" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="AM3" s="34">
         <v>251</v>
       </c>
       <c r="AN3" s="28" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AO3" s="28" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AP3" s="28" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="AQ3" s="29" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="AR3" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="AS3" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="AT3" s="30">
         <v>35591</v>
       </c>
       <c r="AU3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="AV3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="AW3" s="30" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="AX3" s="30" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="AY3" s="30" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="AZ3" s="30" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="BA3" s="30" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="BB3" s="15" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="BC3" s="29" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="BD3" s="29" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="BE3" s="29" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="BF3" s="29" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="BG3" s="18" t="s">
-        <v>105</v>
-      </c>
-      <c r="BH3" s="35" t="s">
-        <v>96</v>
+        <v>108</v>
+      </c>
+      <c r="BH3" s="31" t="s">
+        <v>98</v>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AX2:AX3 Z2:Z3 W2:W3 T2:T3 K2:K3 BF2:BF3" xr:uid="{00000000-0002-0000-0000-000000000000}">
+  <dataValidations count="6">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AX2:AX3">
+      <formula1>INDIRECT($E2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BF2:BF3">
+      <formula1>INDIRECT($E2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K2:K3">
+      <formula1>INDIRECT($E2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T2:T3">
+      <formula1>INDIRECT($E2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W2:W3">
+      <formula1>INDIRECT($E2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Z2:Z3">
       <formula1>INDIRECT($E2)</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="V2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="V3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="V2" r:id="rId1"/>
+    <hyperlink ref="V3" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
--- a/Data/27/testDataIreland.xlsx
+++ b/Data/27/testDataIreland.xlsx
@@ -1,20 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27928"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A95FD54-2D29-47DA-8A69-6299A146CA90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet sheetId="1" name="Sheet1" state="visible" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="106">
   <si>
     <t>TestCaseIDs</t>
   </si>
@@ -190,15 +204,6 @@
     <t>Test_1</t>
   </si>
   <si>
-    <t xml:space="preserve">Test failed for 'Noemy Crooks' Employee:{10699539}TimeoutError: locator.waitFor: Timeout 30000ms exceeded.
-Call log:
-  [2m- waiting for getByRole('button', { name: 'Verify nationality: Onboarding for Noemy Crooks' }).first() to be visible[22m
-</t>
-  </si>
-  <si>
-    <t>Failed</t>
-  </si>
-  <si>
     <t>001 Recruitment (Lubym Wyvyfu (221849))</t>
   </si>
   <si>
@@ -208,10 +213,10 @@
     <t>Mr</t>
   </si>
   <si>
-    <t>Noemy</t>
-  </si>
-  <si>
-    <t>Crooks</t>
+    <t>Joannie</t>
+  </si>
+  <si>
+    <t>Spinka</t>
   </si>
   <si>
     <t>Landline</t>
@@ -280,9 +285,6 @@
     <t>Personal Public Service Number (PPS no)</t>
   </si>
   <si>
-    <t>1234727TW</t>
-  </si>
-  <si>
     <t>Male</t>
   </si>
   <si>
@@ -319,384 +321,6 @@
     <t>Test_2</t>
   </si>
   <si>
-    <t xml:space="preserve">Test failed for 'Ollie Moen' Employee:{10699540}TimeoutError: locator.click: Timeout 30000ms exceeded.
-Call log:
-  [2m- waiting for locator('xpath=(//*[@data-automation-id=\'pex-search-result-header\']//a[contains(text(),\'10699540\')])[1]')[22m
-[2m  -   locator resolved to &lt;a data-uxi-rank="0" class="pexsearch-11mf54b" data…&gt;Ollie Moen (10699540)&lt;/a&gt;[22m
-[2m  - attempting click action[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is not stable[22m
-[2m  - retrying click action, attempt #1[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="css-14h3bs2-ActionButtonsContainer ep60xj…&gt;…&lt;/div&gt; from &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #2[22m
-[2m  -   waiting 20ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="css-14h3bs2-ActionButtonsContainer ep60xj…&gt;…&lt;/div&gt; from &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #3[22m
-[2m  -   waiting 100ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; intercepts pointer events[22m
-[2m  - retrying click action, attempt #4[22m
-[2m  -   waiting 100ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; intercepts pointer events[22m
-[2m  - retrying click action, attempt #5[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="css-14h3bs2-ActionButtonsContainer ep60xj…&gt;…&lt;/div&gt; from &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #6[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="css-14h3bs2-ActionButtonsContainer ep60xj…&gt;…&lt;/div&gt; from &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #7[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; intercepts pointer events[22m
-[2m  - retrying click action, attempt #8[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; intercepts pointer events[22m
-[2m  - retrying click action, attempt #9[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="css-14h3bs2-ActionButtonsContainer ep60xj…&gt;…&lt;/div&gt; from &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #10[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="css-14h3bs2-ActionButtonsContainer ep60xj…&gt;…&lt;/div&gt; from &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #11[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; intercepts pointer events[22m
-[2m  - retrying click action, attempt #12[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; intercepts pointer events[22m
-[2m  - retrying click action, attempt #13[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="css-14h3bs2-ActionButtonsContainer ep60xj…&gt;…&lt;/div&gt; from &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #14[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="css-14h3bs2-ActionButtonsContainer ep60xj…&gt;…&lt;/div&gt; from &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #15[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; intercepts pointer events[22m
-[2m  - retrying click action, attempt #16[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; intercepts pointer events[22m
-[2m  - retrying click action, attempt #17[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="css-14h3bs2-ActionButtonsContainer ep60xj…&gt;…&lt;/div&gt; from &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #18[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="css-14h3bs2-ActionButtonsContainer ep60xj…&gt;…&lt;/div&gt; from &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #19[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; intercepts pointer events[22m
-[2m  - retrying click action, attempt #20[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; intercepts pointer events[22m
-[2m  - retrying click action, attempt #21[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="css-14h3bs2-ActionButtonsContainer ep60xj…&gt;…&lt;/div&gt; from &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #22[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="css-14h3bs2-ActionButtonsContainer ep60xj…&gt;…&lt;/div&gt; from &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #23[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; intercepts pointer events[22m
-[2m  - retrying click action, attempt #24[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; intercepts pointer events[22m
-[2m  - retrying click action, attempt #25[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="css-14h3bs2-ActionButtonsContainer ep60xj…&gt;…&lt;/div&gt; from &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #26[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="css-14h3bs2-ActionButtonsContainer ep60xj…&gt;…&lt;/div&gt; from &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #27[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; intercepts pointer events[22m
-[2m  - retrying click action, attempt #28[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; intercepts pointer events[22m
-[2m  - retrying click action, attempt #29[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="css-14h3bs2-ActionButtonsContainer ep60xj…&gt;…&lt;/div&gt; from &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #30[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="css-14h3bs2-ActionButtonsContainer ep60xj…&gt;…&lt;/div&gt; from &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #31[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; intercepts pointer events[22m
-[2m  - retrying click action, attempt #32[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; intercepts pointer events[22m
-[2m  - retrying click action, attempt #33[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="css-14h3bs2-ActionButtonsContainer ep60xj…&gt;…&lt;/div&gt; from &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #34[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="css-14h3bs2-ActionButtonsContainer ep60xj…&gt;…&lt;/div&gt; from &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #35[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; intercepts pointer events[22m
-[2m  - retrying click action, attempt #36[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; intercepts pointer events[22m
-[2m  - retrying click action, attempt #37[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="css-14h3bs2-ActionButtonsContainer ep60xj…&gt;…&lt;/div&gt; from &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #38[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="css-14h3bs2-ActionButtonsContainer ep60xj…&gt;…&lt;/div&gt; from &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #39[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; intercepts pointer events[22m
-[2m  - retrying click action, attempt #40[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; intercepts pointer events[22m
-[2m  - retrying click action, attempt #41[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="css-14h3bs2-ActionButtonsContainer ep60xj…&gt;…&lt;/div&gt; from &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #42[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="css-14h3bs2-ActionButtonsContainer ep60xj…&gt;…&lt;/div&gt; from &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #43[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; intercepts pointer events[22m
-[2m  - retrying click action, attempt #44[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; intercepts pointer events[22m
-[2m  - retrying click action, attempt #45[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="css-14h3bs2-ActionButtonsContainer ep60xj…&gt;…&lt;/div&gt; from &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #46[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="css-14h3bs2-ActionButtonsContainer ep60xj…&gt;…&lt;/div&gt; from &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #47[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; intercepts pointer events[22m
-[2m  - retrying click action, attempt #48[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; intercepts pointer events[22m
-[2m  - retrying click action, attempt #49[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="css-14h3bs2-ActionButtonsContainer ep60xj…&gt;…&lt;/div&gt; from &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #50[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="css-14h3bs2-ActionButtonsContainer ep60xj…&gt;…&lt;/div&gt; from &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #51[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; intercepts pointer events[22m
-[2m  - retrying click action, attempt #52[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div role="dialog" aria-modal="true" data-popup-versi…&gt;…&lt;/div&gt; intercepts pointer events[22m
-[2m  - retrying click action, attempt #53[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-</t>
-  </si>
-  <si>
     <t>001 Store Management (Savip Gytape (100446))</t>
   </si>
   <si>
@@ -715,75 +339,78 @@
     <t>92 Retail Management</t>
   </si>
   <si>
-    <t>1234728TW</t>
-  </si>
-  <si>
     <t>IE Management Group 20</t>
+  </si>
+  <si>
+    <t>1234732TW</t>
+  </si>
+  <si>
+    <t>1234733TW</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="mm/dd/yyyy"/>
   </numFmts>
   <fonts count="8" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
-      <color theme="1"/>
+      <sz val="11"/>
+      <color theme="9" tint="-0.249977111117893"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="10"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <color rgb="FFFF0000"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <family val="2"/>
-      <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <color theme="9" tint="-0.249977111117893"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <u/>
+      <sz val="11"/>
       <color theme="10"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
+      <sz val="11"/>
       <color rgb="FF4A4A4A"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
+      <sz val="11"/>
       <color rgb="FF000000"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="8">
@@ -801,19 +428,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.5999938962981048"/>
+        <fgColor theme="6" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.1499984740745262"/>
+        <fgColor theme="0" tint="-0.14999847407452621"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.7999816888943144"/>
+        <fgColor theme="5" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -839,15 +466,25 @@
     </border>
     <border>
       <left/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
-      <right style="thin"/>
-      <top style="thin"/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
       <bottom/>
       <diagonal/>
     </border>
@@ -858,15 +495,27 @@
       <right style="medium">
         <color indexed="64"/>
       </right>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -884,7 +533,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -920,7 +569,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1257,9 +905,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:BH3"/>
-  <sheetFormatPr defaultRowHeight="14.5" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.35" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="14.5" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="23.6328125" customWidth="1"/>
     <col min="2" max="2" width="68.08984375" customWidth="1"/>
@@ -1310,7 +958,7 @@
     <col min="100" max="100" width="34.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="51" customHeight="1" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:60" ht="51" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1492,402 +1140,379 @@
         <v>56</v>
       </c>
     </row>
-    <row r="2" ht="87.5" customHeight="1" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:60" ht="87.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>57</v>
       </c>
-      <c r="B2" s="12" t="s">
+      <c r="B2" s="12"/>
+      <c r="C2" s="32"/>
+      <c r="D2" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="C2" s="13" t="s">
+      <c r="E2" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="D2" s="14" t="s">
+      <c r="F2" s="15" t="s">
         <v>60</v>
       </c>
-      <c r="E2" s="15" t="s">
+      <c r="G2" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="F2" s="16" t="s">
+      <c r="H2" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="G2" s="17" t="s">
+      <c r="I2" s="17">
+        <v>861240232</v>
+      </c>
+      <c r="J2" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="H2" s="17" t="s">
+      <c r="K2" s="17" t="s">
         <v>64</v>
       </c>
-      <c r="I2" s="18">
+      <c r="L2" s="18">
+        <f t="shared" ref="L2:L3" ca="1" si="0">TODAY()-31</f>
+        <v>45786</v>
+      </c>
+      <c r="M2" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="N2" s="19" t="s">
+        <v>66</v>
+      </c>
+      <c r="O2" s="19" t="s">
+        <v>67</v>
+      </c>
+      <c r="P2" s="17">
+        <v>38</v>
+      </c>
+      <c r="Q2" s="17" t="s">
+        <v>66</v>
+      </c>
+      <c r="R2" s="17" t="s">
+        <v>68</v>
+      </c>
+      <c r="S2" s="17" t="s">
+        <v>66</v>
+      </c>
+      <c r="T2" s="17" t="s">
+        <v>64</v>
+      </c>
+      <c r="U2" s="20" t="s">
+        <v>69</v>
+      </c>
+      <c r="V2" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="W2" s="17" t="s">
+        <v>64</v>
+      </c>
+      <c r="X2" s="22">
+        <f t="shared" ref="X2:X3" ca="1" si="1">L2</f>
+        <v>45786</v>
+      </c>
+      <c r="Y2" s="18">
+        <f t="shared" ref="Y2:Y3" ca="1" si="2">X2+90</f>
+        <v>45876</v>
+      </c>
+      <c r="Z2" s="17" t="s">
+        <v>71</v>
+      </c>
+      <c r="AA2" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="AB2" s="24" t="s">
+        <v>73</v>
+      </c>
+      <c r="AC2" s="25" t="s">
+        <v>74</v>
+      </c>
+      <c r="AD2" s="24" t="s">
+        <v>75</v>
+      </c>
+      <c r="AE2" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="AF2" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="AG2" s="26">
+        <v>37.5</v>
+      </c>
+      <c r="AH2" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="AI2" t="s">
+        <v>79</v>
+      </c>
+      <c r="AJ2" s="22" t="s">
+        <v>80</v>
+      </c>
+      <c r="AK2" s="17" t="s">
+        <v>81</v>
+      </c>
+      <c r="AL2" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="AM2" t="s">
+        <v>83</v>
+      </c>
+      <c r="AN2" s="27" t="s">
+        <v>80</v>
+      </c>
+      <c r="AO2" s="27" t="s">
+        <v>80</v>
+      </c>
+      <c r="AP2" s="27" t="s">
+        <v>65</v>
+      </c>
+      <c r="AQ2" s="28" t="s">
+        <v>84</v>
+      </c>
+      <c r="AR2" t="s">
+        <v>104</v>
+      </c>
+      <c r="AS2" t="s">
+        <v>85</v>
+      </c>
+      <c r="AT2" s="29">
+        <v>35591</v>
+      </c>
+      <c r="AU2" t="s">
+        <v>65</v>
+      </c>
+      <c r="AV2" t="s">
+        <v>66</v>
+      </c>
+      <c r="AW2" s="29" t="s">
+        <v>66</v>
+      </c>
+      <c r="AX2" s="29" t="s">
+        <v>86</v>
+      </c>
+      <c r="AY2" s="29" t="s">
+        <v>87</v>
+      </c>
+      <c r="AZ2" s="29" t="s">
+        <v>88</v>
+      </c>
+      <c r="BA2" s="29" t="s">
+        <v>65</v>
+      </c>
+      <c r="BB2" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="BC2" s="28" t="s">
+        <v>90</v>
+      </c>
+      <c r="BD2" s="28" t="s">
+        <v>91</v>
+      </c>
+      <c r="BE2" s="28" t="s">
+        <v>92</v>
+      </c>
+      <c r="BF2" s="28" t="s">
+        <v>93</v>
+      </c>
+      <c r="BG2" s="17" t="s">
+        <v>94</v>
+      </c>
+      <c r="BH2" s="30" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="3" spans="1:60" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>96</v>
+      </c>
+      <c r="B3" s="31"/>
+      <c r="C3" s="32"/>
+      <c r="D3" s="13" t="s">
+        <v>97</v>
+      </c>
+      <c r="E3" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="F3" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="G3" t="s">
+        <v>98</v>
+      </c>
+      <c r="H3" t="s">
+        <v>99</v>
+      </c>
+      <c r="I3" s="17">
         <v>861240232</v>
       </c>
-      <c r="J2" s="18" t="s">
+      <c r="J3" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="K3" s="17" t="s">
+        <v>64</v>
+      </c>
+      <c r="L3" s="18">
+        <f t="shared" ca="1" si="0"/>
+        <v>45786</v>
+      </c>
+      <c r="M3" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="K2" s="18" t="s">
+      <c r="N3" s="19" t="s">
         <v>66</v>
       </c>
-      <c r="L2" s="19">
-        <f t="shared" ref="L2:L3" si="0">TODAY()-31</f>
-        <v>45779</v>
-      </c>
-      <c r="M2" s="15" t="s">
+      <c r="O3" s="19" t="s">
         <v>67</v>
       </c>
-      <c r="N2" s="20" t="s">
+      <c r="P3" s="17">
+        <v>38</v>
+      </c>
+      <c r="Q3" s="17" t="s">
+        <v>66</v>
+      </c>
+      <c r="R3" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="O2" s="20" t="s">
+      <c r="S3" s="17" t="s">
+        <v>66</v>
+      </c>
+      <c r="T3" s="17" t="s">
+        <v>64</v>
+      </c>
+      <c r="U3" s="20" t="s">
         <v>69</v>
       </c>
-      <c r="P2" s="18">
-        <v>38</v>
-      </c>
-      <c r="Q2" s="18" t="s">
-        <v>68</v>
-      </c>
-      <c r="R2" s="18" t="s">
+      <c r="V3" s="21" t="s">
         <v>70</v>
       </c>
-      <c r="S2" s="18" t="s">
-        <v>68</v>
-      </c>
-      <c r="T2" s="18" t="s">
+      <c r="W3" s="17" t="s">
+        <v>64</v>
+      </c>
+      <c r="X3" s="22">
+        <f t="shared" ca="1" si="1"/>
+        <v>45786</v>
+      </c>
+      <c r="Y3" s="18">
+        <f t="shared" ca="1" si="2"/>
+        <v>45876</v>
+      </c>
+      <c r="Z3" s="17" t="s">
+        <v>71</v>
+      </c>
+      <c r="AA3" s="23" t="s">
+        <v>100</v>
+      </c>
+      <c r="AB3" s="24" t="s">
+        <v>73</v>
+      </c>
+      <c r="AC3" s="25" t="s">
+        <v>101</v>
+      </c>
+      <c r="AD3" s="24" t="s">
+        <v>75</v>
+      </c>
+      <c r="AE3" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="AF3" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="AG3" s="26">
+        <v>37.5</v>
+      </c>
+      <c r="AH3" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="AI3" t="s">
+        <v>79</v>
+      </c>
+      <c r="AJ3" s="22" t="s">
+        <v>80</v>
+      </c>
+      <c r="AK3" s="17" t="s">
+        <v>81</v>
+      </c>
+      <c r="AL3" s="17" t="s">
+        <v>102</v>
+      </c>
+      <c r="AM3" s="33">
+        <v>251</v>
+      </c>
+      <c r="AN3" s="27" t="s">
+        <v>80</v>
+      </c>
+      <c r="AO3" s="27" t="s">
+        <v>80</v>
+      </c>
+      <c r="AP3" s="27" t="s">
+        <v>65</v>
+      </c>
+      <c r="AQ3" s="28" t="s">
+        <v>84</v>
+      </c>
+      <c r="AR3" t="s">
+        <v>105</v>
+      </c>
+      <c r="AS3" t="s">
+        <v>85</v>
+      </c>
+      <c r="AT3" s="29">
+        <v>35591</v>
+      </c>
+      <c r="AU3" t="s">
+        <v>65</v>
+      </c>
+      <c r="AV3" t="s">
         <v>66</v>
       </c>
-      <c r="U2" s="21" t="s">
-        <v>71</v>
-      </c>
-      <c r="V2" s="22" t="s">
-        <v>72</v>
-      </c>
-      <c r="W2" s="18" t="s">
+      <c r="AW3" s="29" t="s">
         <v>66</v>
       </c>
-      <c r="X2" s="23">
-        <f t="shared" ref="X2:X3" si="1">L2</f>
-        <v>45779</v>
-      </c>
-      <c r="Y2" s="19">
-        <f t="shared" ref="Y2:Y3" si="2">X2+90</f>
-        <v>45869</v>
-      </c>
-      <c r="Z2" s="18" t="s">
-        <v>73</v>
-      </c>
-      <c r="AA2" s="24" t="s">
-        <v>74</v>
-      </c>
-      <c r="AB2" s="25" t="s">
-        <v>75</v>
-      </c>
-      <c r="AC2" s="26" t="s">
-        <v>76</v>
-      </c>
-      <c r="AD2" s="25" t="s">
-        <v>77</v>
-      </c>
-      <c r="AE2" s="15" t="s">
-        <v>78</v>
-      </c>
-      <c r="AF2" s="15" t="s">
-        <v>79</v>
-      </c>
-      <c r="AG2" s="27">
-        <v>37.5</v>
-      </c>
-      <c r="AH2" s="15" t="s">
-        <v>80</v>
-      </c>
-      <c r="AI2" t="s">
-        <v>81</v>
-      </c>
-      <c r="AJ2" s="23" t="s">
-        <v>82</v>
-      </c>
-      <c r="AK2" s="18" t="s">
-        <v>83</v>
-      </c>
-      <c r="AL2" s="18" t="s">
-        <v>84</v>
-      </c>
-      <c r="AM2" t="s">
-        <v>85</v>
-      </c>
-      <c r="AN2" s="28" t="s">
-        <v>82</v>
-      </c>
-      <c r="AO2" s="28" t="s">
-        <v>82</v>
-      </c>
-      <c r="AP2" s="28" t="s">
-        <v>67</v>
-      </c>
-      <c r="AQ2" s="29" t="s">
+      <c r="AX3" s="29" t="s">
         <v>86</v>
       </c>
-      <c r="AR2" t="s">
+      <c r="AY3" s="29" t="s">
         <v>87</v>
       </c>
-      <c r="AS2" t="s">
+      <c r="AZ3" s="29" t="s">
         <v>88</v>
       </c>
-      <c r="AT2" s="30">
-        <v>35591</v>
-      </c>
-      <c r="AU2" t="s">
-        <v>67</v>
-      </c>
-      <c r="AV2" t="s">
-        <v>68</v>
-      </c>
-      <c r="AW2" s="30" t="s">
-        <v>68</v>
-      </c>
-      <c r="AX2" s="30" t="s">
+      <c r="BA3" s="29" t="s">
+        <v>65</v>
+      </c>
+      <c r="BB3" s="14" t="s">
         <v>89</v>
       </c>
-      <c r="AY2" s="30" t="s">
+      <c r="BC3" s="28" t="s">
         <v>90</v>
       </c>
-      <c r="AZ2" s="30" t="s">
+      <c r="BD3" s="28" t="s">
         <v>91</v>
       </c>
-      <c r="BA2" s="30" t="s">
-        <v>67</v>
-      </c>
-      <c r="BB2" s="15" t="s">
+      <c r="BE3" s="28" t="s">
         <v>92</v>
       </c>
-      <c r="BC2" s="29" t="s">
+      <c r="BF3" s="28" t="s">
         <v>93</v>
       </c>
-      <c r="BD2" s="29" t="s">
-        <v>94</v>
-      </c>
-      <c r="BE2" s="29" t="s">
+      <c r="BG3" s="17" t="s">
+        <v>103</v>
+      </c>
+      <c r="BH3" s="30" t="s">
         <v>95</v>
-      </c>
-      <c r="BF2" s="29" t="s">
-        <v>96</v>
-      </c>
-      <c r="BG2" s="18" t="s">
-        <v>97</v>
-      </c>
-      <c r="BH2" s="31" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="3" ht="14.5" customHeight="1" spans="1:60" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>99</v>
-      </c>
-      <c r="B3" s="32" t="s">
-        <v>100</v>
-      </c>
-      <c r="C3" s="33" t="s">
-        <v>59</v>
-      </c>
-      <c r="D3" s="14" t="s">
-        <v>101</v>
-      </c>
-      <c r="E3" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="F3" s="16" t="s">
-        <v>62</v>
-      </c>
-      <c r="G3" t="s">
-        <v>102</v>
-      </c>
-      <c r="H3" t="s">
-        <v>103</v>
-      </c>
-      <c r="I3" s="18">
-        <v>861240232</v>
-      </c>
-      <c r="J3" s="18" t="s">
-        <v>65</v>
-      </c>
-      <c r="K3" s="18" t="s">
-        <v>66</v>
-      </c>
-      <c r="L3" s="19">
-        <f t="shared" si="0"/>
-        <v>45779</v>
-      </c>
-      <c r="M3" s="15" t="s">
-        <v>67</v>
-      </c>
-      <c r="N3" s="20" t="s">
-        <v>68</v>
-      </c>
-      <c r="O3" s="20" t="s">
-        <v>69</v>
-      </c>
-      <c r="P3" s="18">
-        <v>38</v>
-      </c>
-      <c r="Q3" s="18" t="s">
-        <v>68</v>
-      </c>
-      <c r="R3" s="18" t="s">
-        <v>70</v>
-      </c>
-      <c r="S3" s="18" t="s">
-        <v>68</v>
-      </c>
-      <c r="T3" s="18" t="s">
-        <v>66</v>
-      </c>
-      <c r="U3" s="21" t="s">
-        <v>71</v>
-      </c>
-      <c r="V3" s="22" t="s">
-        <v>72</v>
-      </c>
-      <c r="W3" s="18" t="s">
-        <v>66</v>
-      </c>
-      <c r="X3" s="23">
-        <f t="shared" si="1"/>
-        <v>45779</v>
-      </c>
-      <c r="Y3" s="19">
-        <f t="shared" si="2"/>
-        <v>45869</v>
-      </c>
-      <c r="Z3" s="18" t="s">
-        <v>73</v>
-      </c>
-      <c r="AA3" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="AB3" s="25" t="s">
-        <v>75</v>
-      </c>
-      <c r="AC3" s="26" t="s">
-        <v>105</v>
-      </c>
-      <c r="AD3" s="25" t="s">
-        <v>77</v>
-      </c>
-      <c r="AE3" s="15" t="s">
-        <v>78</v>
-      </c>
-      <c r="AF3" s="15" t="s">
-        <v>50</v>
-      </c>
-      <c r="AG3" s="27">
-        <v>37.5</v>
-      </c>
-      <c r="AH3" s="15" t="s">
-        <v>80</v>
-      </c>
-      <c r="AI3" t="s">
-        <v>81</v>
-      </c>
-      <c r="AJ3" s="23" t="s">
-        <v>82</v>
-      </c>
-      <c r="AK3" s="18" t="s">
-        <v>83</v>
-      </c>
-      <c r="AL3" s="18" t="s">
-        <v>106</v>
-      </c>
-      <c r="AM3" s="34">
-        <v>251</v>
-      </c>
-      <c r="AN3" s="28" t="s">
-        <v>82</v>
-      </c>
-      <c r="AO3" s="28" t="s">
-        <v>82</v>
-      </c>
-      <c r="AP3" s="28" t="s">
-        <v>67</v>
-      </c>
-      <c r="AQ3" s="29" t="s">
-        <v>86</v>
-      </c>
-      <c r="AR3" t="s">
-        <v>107</v>
-      </c>
-      <c r="AS3" t="s">
-        <v>88</v>
-      </c>
-      <c r="AT3" s="30">
-        <v>35591</v>
-      </c>
-      <c r="AU3" t="s">
-        <v>67</v>
-      </c>
-      <c r="AV3" t="s">
-        <v>68</v>
-      </c>
-      <c r="AW3" s="30" t="s">
-        <v>68</v>
-      </c>
-      <c r="AX3" s="30" t="s">
-        <v>89</v>
-      </c>
-      <c r="AY3" s="30" t="s">
-        <v>90</v>
-      </c>
-      <c r="AZ3" s="30" t="s">
-        <v>91</v>
-      </c>
-      <c r="BA3" s="30" t="s">
-        <v>67</v>
-      </c>
-      <c r="BB3" s="15" t="s">
-        <v>92</v>
-      </c>
-      <c r="BC3" s="29" t="s">
-        <v>93</v>
-      </c>
-      <c r="BD3" s="29" t="s">
-        <v>94</v>
-      </c>
-      <c r="BE3" s="29" t="s">
-        <v>95</v>
-      </c>
-      <c r="BF3" s="29" t="s">
-        <v>96</v>
-      </c>
-      <c r="BG3" s="18" t="s">
-        <v>108</v>
-      </c>
-      <c r="BH3" s="31" t="s">
-        <v>98</v>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="6">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AX2:AX3">
-      <formula1>INDIRECT($E2)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BF2:BF3">
-      <formula1>INDIRECT($E2)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K2:K3">
-      <formula1>INDIRECT($E2)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T2:T3">
-      <formula1>INDIRECT($E2)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W2:W3">
-      <formula1>INDIRECT($E2)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Z2:Z3">
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AX2:AX3 Z2:Z3 W2:W3 T2:T3 K2:K3 BF2:BF3" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>INDIRECT($E2)</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="V2" r:id="rId1"/>
-    <hyperlink ref="V3" r:id="rId2"/>
+    <hyperlink ref="V2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="V3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295" r:id="rId3"/>
 </worksheet>
 </file>
--- a/Data/27/testDataIreland.xlsx
+++ b/Data/27/testDataIreland.xlsx
@@ -1,34 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27928"/>
-  <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A95FD54-2D29-47DA-8A69-6299A146CA90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet sheetId="1" name="Sheet1" state="visible" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="109">
   <si>
     <t>TestCaseIDs</t>
   </si>
@@ -204,6 +190,12 @@
     <t>Test_1</t>
   </si>
   <si>
+    <t>10699741</t>
+  </si>
+  <si>
+    <t>Passed</t>
+  </si>
+  <si>
     <t>001 Recruitment (Lubym Wyvyfu (221849))</t>
   </si>
   <si>
@@ -213,10 +205,10 @@
     <t>Mr</t>
   </si>
   <si>
-    <t>Joannie</t>
-  </si>
-  <si>
-    <t>Spinka</t>
+    <t>Jayda</t>
+  </si>
+  <si>
+    <t>Lakin</t>
   </si>
   <si>
     <t>Landline</t>
@@ -285,6 +277,9 @@
     <t>Personal Public Service Number (PPS no)</t>
   </si>
   <si>
+    <t>1234735TW</t>
+  </si>
+  <si>
     <t>Male</t>
   </si>
   <si>
@@ -321,16 +316,19 @@
     <t>Test_2</t>
   </si>
   <si>
+    <t>10699757</t>
+  </si>
+  <si>
     <t>001 Store Management (Savip Gytape (100446))</t>
   </si>
   <si>
-    <t>Ollie</t>
-  </si>
-  <si>
-    <t>Moen</t>
-  </si>
-  <si>
-    <t>Auto 59907084</t>
+    <t>Mandy</t>
+  </si>
+  <si>
+    <t>Raynor</t>
+  </si>
+  <si>
+    <t>Auto 16592845</t>
   </si>
   <si>
     <t>Department Manager</t>
@@ -339,78 +337,75 @@
     <t>92 Retail Management</t>
   </si>
   <si>
+    <t>1234738TW</t>
+  </si>
+  <si>
     <t>IE Management Group 20</t>
-  </si>
-  <si>
-    <t>1234732TW</t>
-  </si>
-  <si>
-    <t>1234733TW</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="mm/dd/yyyy"/>
   </numFmts>
   <fonts count="8" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
-      <sz val="10"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="10"/>
+      <name val="Calibri"/>
     </font>
     <font>
-      <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
+      <family val="2"/>
+      <scheme val="minor"/>
       <sz val="11"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <color theme="9" tint="-0.249977111117893"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
-      <color theme="9" tint="-0.249977111117893"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
-      <sz val="11"/>
       <color theme="10"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
-      <sz val="11"/>
       <color rgb="FF4A4A4A"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
-      <sz val="11"/>
       <color rgb="FF000000"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="8">
@@ -428,19 +423,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.59999389629810485"/>
+        <fgColor theme="6" tint="0.5999938962981048"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <fgColor theme="0" tint="-0.1499984740745262"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79998168889431442"/>
+        <fgColor theme="5" tint="0.7999816888943144"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -452,7 +447,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
+        <fgColor rgb="FF00FF00"/>
       </patternFill>
     </fill>
   </fills>
@@ -466,25 +461,15 @@
     </border>
     <border>
       <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
     <border>
       <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
+      <right style="thin"/>
+      <top style="thin"/>
       <bottom/>
       <diagonal/>
     </border>
@@ -495,27 +480,15 @@
       <right style="medium">
         <color indexed="64"/>
       </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <top style="thin"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
     <border>
@@ -533,7 +506,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -566,9 +539,10 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -619,10 +593,6 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -905,9 +875,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:BH3"/>
-  <sheetFormatPr defaultRowHeight="14.5" customHeight="1" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.5" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.35" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="23.6328125" customWidth="1"/>
     <col min="2" max="2" width="68.08984375" customWidth="1"/>
@@ -958,7 +928,7 @@
     <col min="100" max="100" width="34.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:60" ht="51" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" ht="51" customHeight="1" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1140,379 +1110,402 @@
         <v>56</v>
       </c>
     </row>
-    <row r="2" spans="1:60" ht="87.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" ht="87.5" customHeight="1" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>57</v>
       </c>
-      <c r="B2" s="12"/>
-      <c r="C2" s="32"/>
-      <c r="D2" s="13" t="s">
+      <c r="B2" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="E2" s="14" t="s">
+      <c r="C2" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="F2" s="15" t="s">
+      <c r="D2" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="G2" s="16" t="s">
+      <c r="E2" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="H2" s="16" t="s">
+      <c r="F2" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="I2" s="17">
+      <c r="G2" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="H2" s="17" t="s">
+        <v>64</v>
+      </c>
+      <c r="I2" s="18">
         <v>861240232</v>
       </c>
-      <c r="J2" s="17" t="s">
-        <v>63</v>
-      </c>
-      <c r="K2" s="17" t="s">
-        <v>64</v>
-      </c>
-      <c r="L2" s="18">
-        <f t="shared" ref="L2:L3" ca="1" si="0">TODAY()-31</f>
-        <v>45786</v>
-      </c>
-      <c r="M2" s="14" t="s">
+      <c r="J2" s="18" t="s">
         <v>65</v>
       </c>
-      <c r="N2" s="19" t="s">
+      <c r="K2" s="18" t="s">
         <v>66</v>
       </c>
-      <c r="O2" s="19" t="s">
+      <c r="L2" s="19">
+        <f t="shared" ref="L2:L3" si="0">TODAY()-31</f>
+        <v>45795</v>
+      </c>
+      <c r="M2" s="15" t="s">
         <v>67</v>
       </c>
-      <c r="P2" s="17">
+      <c r="N2" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="O2" s="20" t="s">
+        <v>69</v>
+      </c>
+      <c r="P2" s="18">
         <v>38</v>
       </c>
-      <c r="Q2" s="17" t="s">
+      <c r="Q2" s="18" t="s">
+        <v>68</v>
+      </c>
+      <c r="R2" s="18" t="s">
+        <v>70</v>
+      </c>
+      <c r="S2" s="18" t="s">
+        <v>68</v>
+      </c>
+      <c r="T2" s="18" t="s">
         <v>66</v>
       </c>
-      <c r="R2" s="17" t="s">
+      <c r="U2" s="21" t="s">
+        <v>71</v>
+      </c>
+      <c r="V2" s="22" t="s">
+        <v>72</v>
+      </c>
+      <c r="W2" s="18" t="s">
+        <v>66</v>
+      </c>
+      <c r="X2" s="23">
+        <f t="shared" ref="X2:X3" si="1">L2</f>
+        <v>45795</v>
+      </c>
+      <c r="Y2" s="19">
+        <f t="shared" ref="Y2:Y3" si="2">X2+90</f>
+        <v>45885</v>
+      </c>
+      <c r="Z2" s="18" t="s">
+        <v>73</v>
+      </c>
+      <c r="AA2" s="24" t="s">
+        <v>74</v>
+      </c>
+      <c r="AB2" s="25" t="s">
+        <v>75</v>
+      </c>
+      <c r="AC2" s="26" t="s">
+        <v>76</v>
+      </c>
+      <c r="AD2" s="25" t="s">
+        <v>77</v>
+      </c>
+      <c r="AE2" s="15" t="s">
+        <v>78</v>
+      </c>
+      <c r="AF2" s="15" t="s">
+        <v>79</v>
+      </c>
+      <c r="AG2" s="27">
+        <v>37.5</v>
+      </c>
+      <c r="AH2" s="15" t="s">
+        <v>80</v>
+      </c>
+      <c r="AI2" t="s">
+        <v>81</v>
+      </c>
+      <c r="AJ2" s="23" t="s">
+        <v>82</v>
+      </c>
+      <c r="AK2" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="AL2" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="AM2" t="s">
+        <v>85</v>
+      </c>
+      <c r="AN2" s="28" t="s">
+        <v>82</v>
+      </c>
+      <c r="AO2" s="28" t="s">
+        <v>82</v>
+      </c>
+      <c r="AP2" s="28" t="s">
+        <v>67</v>
+      </c>
+      <c r="AQ2" s="29" t="s">
+        <v>86</v>
+      </c>
+      <c r="AR2" t="s">
+        <v>87</v>
+      </c>
+      <c r="AS2" t="s">
+        <v>88</v>
+      </c>
+      <c r="AT2" s="30">
+        <v>35591</v>
+      </c>
+      <c r="AU2" t="s">
+        <v>67</v>
+      </c>
+      <c r="AV2" t="s">
         <v>68</v>
       </c>
-      <c r="S2" s="17" t="s">
+      <c r="AW2" s="30" t="s">
+        <v>68</v>
+      </c>
+      <c r="AX2" s="30" t="s">
+        <v>89</v>
+      </c>
+      <c r="AY2" s="30" t="s">
+        <v>90</v>
+      </c>
+      <c r="AZ2" s="30" t="s">
+        <v>91</v>
+      </c>
+      <c r="BA2" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="BB2" s="15" t="s">
+        <v>92</v>
+      </c>
+      <c r="BC2" s="29" t="s">
+        <v>93</v>
+      </c>
+      <c r="BD2" s="29" t="s">
+        <v>94</v>
+      </c>
+      <c r="BE2" s="29" t="s">
+        <v>95</v>
+      </c>
+      <c r="BF2" s="29" t="s">
+        <v>96</v>
+      </c>
+      <c r="BG2" s="18" t="s">
+        <v>97</v>
+      </c>
+      <c r="BH2" s="31" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="3" ht="14.5" customHeight="1" spans="1:60" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="C3" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="D3" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="E3" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="F3" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="G3" t="s">
+        <v>102</v>
+      </c>
+      <c r="H3" t="s">
+        <v>103</v>
+      </c>
+      <c r="I3" s="18">
+        <v>861240232</v>
+      </c>
+      <c r="J3" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="K3" s="18" t="s">
         <v>66</v>
       </c>
-      <c r="T2" s="17" t="s">
-        <v>64</v>
-      </c>
-      <c r="U2" s="20" t="s">
+      <c r="L3" s="19">
+        <f t="shared" si="0"/>
+        <v>45795</v>
+      </c>
+      <c r="M3" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="N3" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="O3" s="20" t="s">
         <v>69</v>
       </c>
-      <c r="V2" s="21" t="s">
+      <c r="P3" s="18">
+        <v>38</v>
+      </c>
+      <c r="Q3" s="18" t="s">
+        <v>68</v>
+      </c>
+      <c r="R3" s="18" t="s">
         <v>70</v>
       </c>
-      <c r="W2" s="17" t="s">
-        <v>64</v>
-      </c>
-      <c r="X2" s="22">
-        <f t="shared" ref="X2:X3" ca="1" si="1">L2</f>
-        <v>45786</v>
-      </c>
-      <c r="Y2" s="18">
-        <f t="shared" ref="Y2:Y3" ca="1" si="2">X2+90</f>
-        <v>45876</v>
-      </c>
-      <c r="Z2" s="17" t="s">
+      <c r="S3" s="18" t="s">
+        <v>68</v>
+      </c>
+      <c r="T3" s="18" t="s">
+        <v>66</v>
+      </c>
+      <c r="U3" s="21" t="s">
         <v>71</v>
       </c>
-      <c r="AA2" s="23" t="s">
+      <c r="V3" s="22" t="s">
         <v>72</v>
       </c>
-      <c r="AB2" s="24" t="s">
+      <c r="W3" s="18" t="s">
+        <v>66</v>
+      </c>
+      <c r="X3" s="23">
+        <f t="shared" si="1"/>
+        <v>45795</v>
+      </c>
+      <c r="Y3" s="19">
+        <f t="shared" si="2"/>
+        <v>45885</v>
+      </c>
+      <c r="Z3" s="18" t="s">
         <v>73</v>
       </c>
-      <c r="AC2" s="25" t="s">
-        <v>74</v>
-      </c>
-      <c r="AD2" s="24" t="s">
+      <c r="AA3" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="AB3" s="25" t="s">
         <v>75</v>
       </c>
-      <c r="AE2" s="14" t="s">
-        <v>76</v>
-      </c>
-      <c r="AF2" s="14" t="s">
+      <c r="AC3" s="26" t="s">
+        <v>105</v>
+      </c>
+      <c r="AD3" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="AG2" s="26">
+      <c r="AE3" s="15" t="s">
+        <v>78</v>
+      </c>
+      <c r="AF3" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="AG3" s="27">
         <v>37.5</v>
       </c>
-      <c r="AH2" s="14" t="s">
-        <v>78</v>
-      </c>
-      <c r="AI2" t="s">
-        <v>79</v>
-      </c>
-      <c r="AJ2" s="22" t="s">
+      <c r="AH3" s="15" t="s">
         <v>80</v>
       </c>
-      <c r="AK2" s="17" t="s">
+      <c r="AI3" t="s">
         <v>81</v>
       </c>
-      <c r="AL2" s="17" t="s">
+      <c r="AJ3" s="23" t="s">
         <v>82</v>
       </c>
-      <c r="AM2" t="s">
+      <c r="AK3" s="18" t="s">
         <v>83</v>
       </c>
-      <c r="AN2" s="27" t="s">
-        <v>80</v>
-      </c>
-      <c r="AO2" s="27" t="s">
-        <v>80</v>
-      </c>
-      <c r="AP2" s="27" t="s">
-        <v>65</v>
-      </c>
-      <c r="AQ2" s="28" t="s">
-        <v>84</v>
-      </c>
-      <c r="AR2" t="s">
-        <v>104</v>
-      </c>
-      <c r="AS2" t="s">
-        <v>85</v>
-      </c>
-      <c r="AT2" s="29">
+      <c r="AL3" s="18" t="s">
+        <v>106</v>
+      </c>
+      <c r="AM3" s="32">
+        <v>251</v>
+      </c>
+      <c r="AN3" s="28" t="s">
+        <v>82</v>
+      </c>
+      <c r="AO3" s="28" t="s">
+        <v>82</v>
+      </c>
+      <c r="AP3" s="28" t="s">
+        <v>67</v>
+      </c>
+      <c r="AQ3" s="29" t="s">
+        <v>86</v>
+      </c>
+      <c r="AR3" t="s">
+        <v>107</v>
+      </c>
+      <c r="AS3" t="s">
+        <v>88</v>
+      </c>
+      <c r="AT3" s="30">
         <v>35591</v>
       </c>
-      <c r="AU2" t="s">
-        <v>65</v>
-      </c>
-      <c r="AV2" t="s">
-        <v>66</v>
-      </c>
-      <c r="AW2" s="29" t="s">
-        <v>66</v>
-      </c>
-      <c r="AX2" s="29" t="s">
-        <v>86</v>
-      </c>
-      <c r="AY2" s="29" t="s">
-        <v>87</v>
-      </c>
-      <c r="AZ2" s="29" t="s">
-        <v>88</v>
-      </c>
-      <c r="BA2" s="29" t="s">
-        <v>65</v>
-      </c>
-      <c r="BB2" s="14" t="s">
+      <c r="AU3" t="s">
+        <v>67</v>
+      </c>
+      <c r="AV3" t="s">
+        <v>68</v>
+      </c>
+      <c r="AW3" s="30" t="s">
+        <v>68</v>
+      </c>
+      <c r="AX3" s="30" t="s">
         <v>89</v>
       </c>
-      <c r="BC2" s="28" t="s">
+      <c r="AY3" s="30" t="s">
         <v>90</v>
       </c>
-      <c r="BD2" s="28" t="s">
+      <c r="AZ3" s="30" t="s">
         <v>91</v>
       </c>
-      <c r="BE2" s="28" t="s">
+      <c r="BA3" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="BB3" s="15" t="s">
         <v>92</v>
       </c>
-      <c r="BF2" s="28" t="s">
+      <c r="BC3" s="29" t="s">
         <v>93</v>
       </c>
-      <c r="BG2" s="17" t="s">
+      <c r="BD3" s="29" t="s">
         <v>94</v>
       </c>
-      <c r="BH2" s="30" t="s">
+      <c r="BE3" s="29" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="3" spans="1:60" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
+      <c r="BF3" s="29" t="s">
         <v>96</v>
       </c>
-      <c r="B3" s="31"/>
-      <c r="C3" s="32"/>
-      <c r="D3" s="13" t="s">
-        <v>97</v>
-      </c>
-      <c r="E3" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="F3" s="15" t="s">
-        <v>60</v>
-      </c>
-      <c r="G3" t="s">
+      <c r="BG3" s="18" t="s">
+        <v>108</v>
+      </c>
+      <c r="BH3" s="31" t="s">
         <v>98</v>
-      </c>
-      <c r="H3" t="s">
-        <v>99</v>
-      </c>
-      <c r="I3" s="17">
-        <v>861240232</v>
-      </c>
-      <c r="J3" s="17" t="s">
-        <v>63</v>
-      </c>
-      <c r="K3" s="17" t="s">
-        <v>64</v>
-      </c>
-      <c r="L3" s="18">
-        <f t="shared" ca="1" si="0"/>
-        <v>45786</v>
-      </c>
-      <c r="M3" s="14" t="s">
-        <v>65</v>
-      </c>
-      <c r="N3" s="19" t="s">
-        <v>66</v>
-      </c>
-      <c r="O3" s="19" t="s">
-        <v>67</v>
-      </c>
-      <c r="P3" s="17">
-        <v>38</v>
-      </c>
-      <c r="Q3" s="17" t="s">
-        <v>66</v>
-      </c>
-      <c r="R3" s="17" t="s">
-        <v>68</v>
-      </c>
-      <c r="S3" s="17" t="s">
-        <v>66</v>
-      </c>
-      <c r="T3" s="17" t="s">
-        <v>64</v>
-      </c>
-      <c r="U3" s="20" t="s">
-        <v>69</v>
-      </c>
-      <c r="V3" s="21" t="s">
-        <v>70</v>
-      </c>
-      <c r="W3" s="17" t="s">
-        <v>64</v>
-      </c>
-      <c r="X3" s="22">
-        <f t="shared" ca="1" si="1"/>
-        <v>45786</v>
-      </c>
-      <c r="Y3" s="18">
-        <f t="shared" ca="1" si="2"/>
-        <v>45876</v>
-      </c>
-      <c r="Z3" s="17" t="s">
-        <v>71</v>
-      </c>
-      <c r="AA3" s="23" t="s">
-        <v>100</v>
-      </c>
-      <c r="AB3" s="24" t="s">
-        <v>73</v>
-      </c>
-      <c r="AC3" s="25" t="s">
-        <v>101</v>
-      </c>
-      <c r="AD3" s="24" t="s">
-        <v>75</v>
-      </c>
-      <c r="AE3" s="14" t="s">
-        <v>76</v>
-      </c>
-      <c r="AF3" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="AG3" s="26">
-        <v>37.5</v>
-      </c>
-      <c r="AH3" s="14" t="s">
-        <v>78</v>
-      </c>
-      <c r="AI3" t="s">
-        <v>79</v>
-      </c>
-      <c r="AJ3" s="22" t="s">
-        <v>80</v>
-      </c>
-      <c r="AK3" s="17" t="s">
-        <v>81</v>
-      </c>
-      <c r="AL3" s="17" t="s">
-        <v>102</v>
-      </c>
-      <c r="AM3" s="33">
-        <v>251</v>
-      </c>
-      <c r="AN3" s="27" t="s">
-        <v>80</v>
-      </c>
-      <c r="AO3" s="27" t="s">
-        <v>80</v>
-      </c>
-      <c r="AP3" s="27" t="s">
-        <v>65</v>
-      </c>
-      <c r="AQ3" s="28" t="s">
-        <v>84</v>
-      </c>
-      <c r="AR3" t="s">
-        <v>105</v>
-      </c>
-      <c r="AS3" t="s">
-        <v>85</v>
-      </c>
-      <c r="AT3" s="29">
-        <v>35591</v>
-      </c>
-      <c r="AU3" t="s">
-        <v>65</v>
-      </c>
-      <c r="AV3" t="s">
-        <v>66</v>
-      </c>
-      <c r="AW3" s="29" t="s">
-        <v>66</v>
-      </c>
-      <c r="AX3" s="29" t="s">
-        <v>86</v>
-      </c>
-      <c r="AY3" s="29" t="s">
-        <v>87</v>
-      </c>
-      <c r="AZ3" s="29" t="s">
-        <v>88</v>
-      </c>
-      <c r="BA3" s="29" t="s">
-        <v>65</v>
-      </c>
-      <c r="BB3" s="14" t="s">
-        <v>89</v>
-      </c>
-      <c r="BC3" s="28" t="s">
-        <v>90</v>
-      </c>
-      <c r="BD3" s="28" t="s">
-        <v>91</v>
-      </c>
-      <c r="BE3" s="28" t="s">
-        <v>92</v>
-      </c>
-      <c r="BF3" s="28" t="s">
-        <v>93</v>
-      </c>
-      <c r="BG3" s="17" t="s">
-        <v>103</v>
-      </c>
-      <c r="BH3" s="30" t="s">
-        <v>95</v>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AX2:AX3 Z2:Z3 W2:W3 T2:T3 K2:K3 BF2:BF3" xr:uid="{00000000-0002-0000-0000-000000000000}">
+  <dataValidations count="6">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AX2:AX3">
+      <formula1>INDIRECT($E2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BF2:BF3">
+      <formula1>INDIRECT($E2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K2:K3">
+      <formula1>INDIRECT($E2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T2:T3">
+      <formula1>INDIRECT($E2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W2:W3">
+      <formula1>INDIRECT($E2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Z2:Z3">
       <formula1>INDIRECT($E2)</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="V2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="V3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="V2" r:id="rId1"/>
+    <hyperlink ref="V3" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295" r:id="rId3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>